--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,479 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124802541</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565559</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6956389</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124802546</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565685</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6956466</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska barkfläk trolig tth</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124802544</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565617</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6956456</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124802543</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565571</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6956409</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>färska försiktiga barkfläk, trol tth</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802541</v>
+        <v>124802543</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565559</v>
+        <v>565571</v>
       </c>
       <c r="R5" t="n">
-        <v>6956389</v>
+        <v>6956409</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1061,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,7 +1066,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,24 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R6" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802544</v>
+        <v>124802541</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,37 +1231,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565617</v>
+        <v>565559</v>
       </c>
       <c r="R7" t="n">
-        <v>6956456</v>
+        <v>6956389</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1371,16 +1366,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R8" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1015,16 +1015,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R5" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,12 +1071,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802544</v>
+        <v>124802541</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,37 +1119,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565617</v>
+        <v>565559</v>
       </c>
       <c r="R6" t="n">
-        <v>6956456</v>
+        <v>6956389</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802541</v>
+        <v>124802544</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,42 +1236,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565559</v>
+        <v>565617</v>
       </c>
       <c r="R7" t="n">
-        <v>6956389</v>
+        <v>6956456</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802546</v>
+        <v>124802543</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1366,21 +1371,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565685</v>
+        <v>565571</v>
       </c>
       <c r="R8" t="n">
-        <v>6956466</v>
+        <v>6956409</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -981,14 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802546</v>
+        <v>124802541</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -997,27 +997,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565685</v>
+        <v>565559</v>
       </c>
       <c r="R5" t="n">
-        <v>6956466</v>
+        <v>6956389</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1071,12 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,14 +1098,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802541</v>
+        <v>124802546</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1119,27 +1114,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565559</v>
+        <v>565685</v>
       </c>
       <c r="R6" t="n">
-        <v>6956389</v>
+        <v>6956466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,24 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R6" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802544</v>
+        <v>124802546</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1254,19 +1249,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565617</v>
+        <v>565685</v>
       </c>
       <c r="R7" t="n">
-        <v>6956456</v>
+        <v>6956466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802546</v>
+        <v>124802543</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1249,21 +1249,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565685</v>
+        <v>565571</v>
       </c>
       <c r="R7" t="n">
-        <v>6956466</v>
+        <v>6956409</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1371,16 +1366,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R8" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802544</v>
+        <v>124802546</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,19 +1132,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565617</v>
+        <v>565685</v>
       </c>
       <c r="R6" t="n">
-        <v>6956456</v>
+        <v>6956466</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1366,24 +1371,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R8" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802543</v>
+        <v>124802544</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565571</v>
+        <v>565617</v>
       </c>
       <c r="R7" t="n">
-        <v>6956409</v>
+        <v>6956456</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802544</v>
+        <v>124802543</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565617</v>
+        <v>565571</v>
       </c>
       <c r="R8" t="n">
-        <v>6956456</v>
+        <v>6956409</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,24 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R6" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802544</v>
+        <v>124802543</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1260,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565617</v>
+        <v>565571</v>
       </c>
       <c r="R7" t="n">
-        <v>6956456</v>
+        <v>6956409</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1371,16 +1366,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R8" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802546</v>
+        <v>124802543</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,21 +1132,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565685</v>
+        <v>565571</v>
       </c>
       <c r="R6" t="n">
-        <v>6956466</v>
+        <v>6956409</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1254,16 +1249,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R7" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1132,16 +1132,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R6" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1249,24 +1254,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R7" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802544</v>
+        <v>124802543</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565617</v>
+        <v>565571</v>
       </c>
       <c r="R8" t="n">
-        <v>6956456</v>
+        <v>6956409</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>124802541</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,24 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R6" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802544</v>
+        <v>124802546</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,19 +1249,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565617</v>
+        <v>565685</v>
       </c>
       <c r="R7" t="n">
-        <v>6956456</v>
+        <v>6956466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1340,7 @@
         <v>124802543</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802544</v>
+        <v>124802543</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565617</v>
+        <v>565571</v>
       </c>
       <c r="R6" t="n">
-        <v>6956456</v>
+        <v>6956409</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802546</v>
+        <v>124802544</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1249,24 +1249,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565685</v>
+        <v>565617</v>
       </c>
       <c r="R7" t="n">
-        <v>6956466</v>
+        <v>6956456</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802543</v>
+        <v>124802546</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1371,16 +1366,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565571</v>
+        <v>565685</v>
       </c>
       <c r="R8" t="n">
-        <v>6956409</v>
+        <v>6956466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1098,16 +1098,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802543</v>
+        <v>124802544</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1138,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565571</v>
+        <v>565617</v>
       </c>
       <c r="R6" t="n">
-        <v>6956409</v>
+        <v>6956456</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,12 +1178,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska försiktiga barkfläk, trol tth</t>
+          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,16 +1210,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802544</v>
+        <v>124802546</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1249,19 +1239,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565617</v>
+        <v>565685</v>
       </c>
       <c r="R7" t="n">
-        <v>6956456</v>
+        <v>6956466</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,12 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ev bohål 3m upp granhögstubbe hålet som swixtrugan</t>
+          <t>färska barkfläk trolig tth</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,16 +1327,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802546</v>
+        <v>124802543</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1366,21 +1356,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565685</v>
+        <v>565571</v>
       </c>
       <c r="R8" t="n">
-        <v>6956466</v>
+        <v>6956409</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska barkfläk trolig tth</t>
+          <t>färska försiktiga barkfläk, trol tth</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1437,6 +1437,964 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126242550</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>565714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6956508</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>04:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>trumningar under 5 minuter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126243167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>565333</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6956297</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126243160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>565443</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6956173</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126242548</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57812</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>565746</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6956514</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126243172</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>565427</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6956436</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126243173</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>565445</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6956437</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126243166</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>565291</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6956336</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126243171</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>565457</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6956321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126243162</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bodåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>565338</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6956203</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1661,7 +1661,7 @@
         <v>126243160</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>126243160</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>126242548</v>
       </c>
       <c r="B12" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>126243173</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>126243166</v>
       </c>
       <c r="B15" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>126243171</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>126243160</v>
       </c>
       <c r="B11" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>126242548</v>
       </c>
       <c r="B12" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>126243173</v>
       </c>
       <c r="B14" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>126243166</v>
       </c>
       <c r="B15" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>126243171</v>
       </c>
       <c r="B16" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 32725-2023 artfynd.xlsx
+++ b/artfynd/A 32725-2023 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>126242550</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>126243167</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126243172</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>126243162</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
